--- a/data/monthly_place/【2025年8月】月次配置.xlsx
+++ b/data/monthly_place/【2025年8月】月次配置.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="612" yWindow="600" windowWidth="21792" windowHeight="10812"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="69">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -101,32 +100,150 @@
     <t>ランディングページビューの単価 (JPY)</t>
   </si>
   <si>
-    <t>No data available.</t>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>広告セット予算を使用</t>
+  </si>
+  <si>
+    <t>actions:link_click</t>
+  </si>
+  <si>
+    <t>クリックから7日間、または表示から1日間</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>アプリ内</t>
+  </si>
+  <si>
+    <t>Instagramストーリーズ</t>
+  </si>
+  <si>
+    <t>Instagram</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>Instagram検索結果</t>
+  </si>
+  <si>
+    <t>Instagramリール</t>
+  </si>
+  <si>
+    <t>発見ホーム</t>
+  </si>
+  <si>
+    <t>発見</t>
+  </si>
+  <si>
+    <t>フィード</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>モバイルウェブ</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>inactive</t>
+  </si>
+  <si>
+    <t>金町駅前ジャスミン歯科</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（マウスピース矯正）</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -134,36 +251,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -452,14 +569,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AB88"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -545,23 +659,6397 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2">
+        <v>14</v>
+      </c>
+      <c r="L2">
+        <v>1.142857</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>38</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R2">
+        <v>16</v>
+      </c>
+      <c r="S2">
+        <v>2375</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>67</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1000</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4">
+        <v>72</v>
+      </c>
+      <c r="L4">
+        <v>1.4305559999999999</v>
+      </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>85</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>67</v>
+      </c>
+      <c r="R4">
+        <v>103</v>
+      </c>
+      <c r="S4">
+        <v>825.24271799999997</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5">
+        <v>63</v>
+      </c>
+      <c r="J5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5">
+        <v>1976</v>
+      </c>
+      <c r="L5">
+        <v>3.4746959999999998</v>
+      </c>
+      <c r="M5">
+        <v>85.301587299999994</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>5374</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>67</v>
+      </c>
+      <c r="R5">
+        <v>6866</v>
+      </c>
+      <c r="S5">
+        <v>782.69734900000003</v>
+      </c>
+      <c r="T5">
+        <v>63</v>
+      </c>
+      <c r="V5">
+        <v>85.301586999999998</v>
+      </c>
+      <c r="W5">
+        <v>0.91756499999999996</v>
+      </c>
+      <c r="X5">
+        <v>66</v>
+      </c>
+      <c r="Y5">
+        <v>0.96125799999999995</v>
+      </c>
+      <c r="Z5">
+        <v>81.424242000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6">
+        <v>108</v>
+      </c>
+      <c r="L6">
+        <v>1.0833330000000001</v>
+      </c>
+      <c r="M6">
+        <v>84.333333330000002</v>
+      </c>
+      <c r="N6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>253</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>65</v>
+      </c>
+      <c r="R6">
+        <v>117</v>
+      </c>
+      <c r="S6">
+        <v>2162.3931619999998</v>
+      </c>
+      <c r="T6">
+        <v>3</v>
+      </c>
+      <c r="V6">
+        <v>84.333332999999996</v>
+      </c>
+      <c r="W6">
+        <v>2.5641029999999998</v>
+      </c>
+      <c r="X6">
+        <v>2</v>
+      </c>
+      <c r="Y6">
+        <v>1.7094020000000001</v>
+      </c>
+      <c r="Z6">
+        <v>126.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>72</v>
+      </c>
+      <c r="L7">
+        <v>1.1666669999999999</v>
+      </c>
+      <c r="N7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>51</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>65</v>
+      </c>
+      <c r="R7">
+        <v>84</v>
+      </c>
+      <c r="S7">
+        <v>607.14285700000005</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>65</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9">
+        <v>101</v>
+      </c>
+      <c r="L9">
+        <v>1.1584159999999999</v>
+      </c>
+      <c r="M9">
+        <v>81</v>
+      </c>
+      <c r="N9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>81</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>65</v>
+      </c>
+      <c r="R9">
+        <v>117</v>
+      </c>
+      <c r="S9">
+        <v>692.30769199999997</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>81</v>
+      </c>
+      <c r="W9">
+        <v>0.85470100000000004</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>0.85470100000000004</v>
+      </c>
+      <c r="Z9">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10">
+        <v>95</v>
+      </c>
+      <c r="J10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10">
+        <v>5168</v>
+      </c>
+      <c r="L10">
+        <v>1.4216329999999999</v>
+      </c>
+      <c r="M10">
+        <v>57.642105260000001</v>
+      </c>
+      <c r="N10" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>5476</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>65</v>
+      </c>
+      <c r="R10">
+        <v>7347</v>
+      </c>
+      <c r="S10">
+        <v>745.33823299999995</v>
+      </c>
+      <c r="T10">
+        <v>95</v>
+      </c>
+      <c r="V10">
+        <v>57.642105000000001</v>
+      </c>
+      <c r="W10">
+        <v>1.293045</v>
+      </c>
+      <c r="X10">
+        <v>103</v>
+      </c>
+      <c r="Y10">
+        <v>1.4019330000000001</v>
+      </c>
+      <c r="Z10">
+        <v>53.165049000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11">
+        <v>32</v>
+      </c>
+      <c r="J11" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11">
+        <v>1430</v>
+      </c>
+      <c r="L11">
+        <v>1.2825169999999999</v>
+      </c>
+      <c r="M11">
+        <v>51.25</v>
+      </c>
+      <c r="N11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1640</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>62</v>
+      </c>
+      <c r="R11">
+        <v>1834</v>
+      </c>
+      <c r="S11">
+        <v>894.22028399999999</v>
+      </c>
+      <c r="T11">
+        <v>32</v>
+      </c>
+      <c r="V11">
+        <v>51.25</v>
+      </c>
+      <c r="W11">
+        <v>1.74482</v>
+      </c>
+      <c r="X11">
+        <v>39</v>
+      </c>
+      <c r="Y11">
+        <v>2.1264989999999999</v>
+      </c>
+      <c r="Z11">
+        <v>42.051282</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12">
+        <v>343</v>
+      </c>
+      <c r="L12">
+        <v>1.2069970000000001</v>
+      </c>
+      <c r="M12">
+        <v>46.2</v>
+      </c>
+      <c r="N12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>231</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>62</v>
+      </c>
+      <c r="R12">
+        <v>414</v>
+      </c>
+      <c r="S12">
+        <v>557.97101399999997</v>
+      </c>
+      <c r="T12">
+        <v>5</v>
+      </c>
+      <c r="V12">
+        <v>46.2</v>
+      </c>
+      <c r="W12">
+        <v>1.2077290000000001</v>
+      </c>
+      <c r="X12">
+        <v>5</v>
+      </c>
+      <c r="Y12">
+        <v>1.2077290000000001</v>
+      </c>
+      <c r="Z12">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13">
+        <v>19</v>
+      </c>
+      <c r="L13">
+        <v>1.1052630000000001</v>
+      </c>
+      <c r="N13" t="s">
+        <v>29</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>8</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>62</v>
+      </c>
+      <c r="R13">
+        <v>21</v>
+      </c>
+      <c r="S13">
+        <v>380.952381</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14">
+        <v>8</v>
+      </c>
+      <c r="J14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14">
+        <v>383</v>
+      </c>
+      <c r="L14">
+        <v>1.156658</v>
+      </c>
+      <c r="M14">
+        <v>36.375</v>
+      </c>
+      <c r="N14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>291</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>62</v>
+      </c>
+      <c r="R14">
+        <v>443</v>
+      </c>
+      <c r="S14">
+        <v>656.88487599999996</v>
+      </c>
+      <c r="T14">
+        <v>8</v>
+      </c>
+      <c r="V14">
+        <v>36.375</v>
+      </c>
+      <c r="W14">
+        <v>1.8058689999999999</v>
+      </c>
+      <c r="X14">
+        <v>11</v>
+      </c>
+      <c r="Y14">
+        <v>2.4830700000000001</v>
+      </c>
+      <c r="Z14">
+        <v>26.454545</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15">
+        <v>66</v>
+      </c>
+      <c r="J15" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15">
+        <v>2998</v>
+      </c>
+      <c r="L15">
+        <v>1.262842</v>
+      </c>
+      <c r="M15">
+        <v>56.575757580000001</v>
+      </c>
+      <c r="N15" t="s">
+        <v>29</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>3734</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>62</v>
+      </c>
+      <c r="R15">
+        <v>3786</v>
+      </c>
+      <c r="S15">
+        <v>986.26518799999997</v>
+      </c>
+      <c r="T15">
+        <v>66</v>
+      </c>
+      <c r="V15">
+        <v>56.575758</v>
+      </c>
+      <c r="W15">
+        <v>1.7432650000000001</v>
+      </c>
+      <c r="X15">
+        <v>72</v>
+      </c>
+      <c r="Y15">
+        <v>1.901743</v>
+      </c>
+      <c r="Z15">
+        <v>51.861111000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="N16" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>62</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1000</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17">
+        <v>14</v>
+      </c>
+      <c r="J17" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17">
+        <v>374</v>
+      </c>
+      <c r="L17">
+        <v>1.2941180000000001</v>
+      </c>
+      <c r="M17">
+        <v>22.85714286</v>
+      </c>
+      <c r="N17" t="s">
+        <v>29</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>320</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>62</v>
+      </c>
+      <c r="R17">
+        <v>484</v>
+      </c>
+      <c r="S17">
+        <v>661.15702499999998</v>
+      </c>
+      <c r="T17">
+        <v>14</v>
+      </c>
+      <c r="V17">
+        <v>22.857143000000001</v>
+      </c>
+      <c r="W17">
+        <v>2.8925619999999999</v>
+      </c>
+      <c r="X17">
+        <v>18</v>
+      </c>
+      <c r="Y17">
+        <v>3.7190080000000001</v>
+      </c>
+      <c r="Z17">
+        <v>17.777778000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18">
+        <v>82</v>
+      </c>
+      <c r="L18">
+        <v>1.2804880000000001</v>
+      </c>
+      <c r="M18">
+        <v>42</v>
+      </c>
+      <c r="N18" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>42</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>62</v>
+      </c>
+      <c r="R18">
+        <v>105</v>
+      </c>
+      <c r="S18">
+        <v>400</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>42</v>
+      </c>
+      <c r="W18">
+        <v>0.95238100000000003</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>0.95238100000000003</v>
+      </c>
+      <c r="Z18">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19">
+        <v>41</v>
+      </c>
+      <c r="L19">
+        <v>1.2195119999999999</v>
+      </c>
+      <c r="N19" t="s">
+        <v>29</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>7</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>62</v>
+      </c>
+      <c r="R19">
+        <v>50</v>
+      </c>
+      <c r="S19">
+        <v>140</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20">
+        <v>9</v>
+      </c>
+      <c r="J20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20">
+        <v>177</v>
+      </c>
+      <c r="L20">
+        <v>1.1299440000000001</v>
+      </c>
+      <c r="M20">
+        <v>13.88888889</v>
+      </c>
+      <c r="N20" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>125</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>62</v>
+      </c>
+      <c r="R20">
+        <v>200</v>
+      </c>
+      <c r="S20">
+        <v>625</v>
+      </c>
+      <c r="T20">
+        <v>9</v>
+      </c>
+      <c r="V20">
+        <v>13.888889000000001</v>
+      </c>
+      <c r="W20">
+        <v>4.5</v>
+      </c>
+      <c r="X20">
+        <v>12</v>
+      </c>
+      <c r="Y20">
+        <v>6</v>
+      </c>
+      <c r="Z20">
+        <v>10.416667</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21">
+        <v>318</v>
+      </c>
+      <c r="J21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21">
+        <v>3784</v>
+      </c>
+      <c r="L21">
+        <v>1.3226739999999999</v>
+      </c>
+      <c r="M21">
+        <v>16.279874209999999</v>
+      </c>
+      <c r="N21" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>5177</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>62</v>
+      </c>
+      <c r="R21">
+        <v>5005</v>
+      </c>
+      <c r="S21">
+        <v>1034.365634</v>
+      </c>
+      <c r="T21">
+        <v>318</v>
+      </c>
+      <c r="V21">
+        <v>16.279874</v>
+      </c>
+      <c r="W21">
+        <v>6.3536460000000003</v>
+      </c>
+      <c r="X21">
+        <v>348</v>
+      </c>
+      <c r="Y21">
+        <v>6.9530469999999998</v>
+      </c>
+      <c r="Z21">
+        <v>14.876436999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H22" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22">
+        <v>63</v>
+      </c>
+      <c r="J22" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22">
+        <v>1569</v>
+      </c>
+      <c r="L22">
+        <v>1.6112169999999999</v>
+      </c>
+      <c r="M22">
+        <v>45.158730159999998</v>
+      </c>
+      <c r="N22" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>2845</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>60</v>
+      </c>
+      <c r="R22">
+        <v>2528</v>
+      </c>
+      <c r="S22">
+        <v>1125.3955699999999</v>
+      </c>
+      <c r="T22">
+        <v>63</v>
+      </c>
+      <c r="V22">
+        <v>45.158729999999998</v>
+      </c>
+      <c r="W22">
+        <v>2.492089</v>
+      </c>
+      <c r="X22">
+        <v>69</v>
+      </c>
+      <c r="Y22">
+        <v>2.7294299999999998</v>
+      </c>
+      <c r="Z22">
+        <v>41.231884000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="N23" t="s">
+        <v>29</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>60</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>2000</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24">
+        <v>9</v>
+      </c>
+      <c r="J24" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24">
+        <v>387</v>
+      </c>
+      <c r="L24">
+        <v>1.3333330000000001</v>
+      </c>
+      <c r="M24">
+        <v>38.444444439999998</v>
+      </c>
+      <c r="N24" t="s">
+        <v>29</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>346</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>60</v>
+      </c>
+      <c r="R24">
+        <v>516</v>
+      </c>
+      <c r="S24">
+        <v>670.54263600000002</v>
+      </c>
+      <c r="T24">
+        <v>9</v>
+      </c>
+      <c r="V24">
+        <v>38.444443999999997</v>
+      </c>
+      <c r="W24">
+        <v>1.744186</v>
+      </c>
+      <c r="X24">
+        <v>10</v>
+      </c>
+      <c r="Y24">
+        <v>1.9379850000000001</v>
+      </c>
+      <c r="Z24">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25">
+        <v>5</v>
+      </c>
+      <c r="J25" t="s">
+        <v>30</v>
+      </c>
+      <c r="K25">
+        <v>210</v>
+      </c>
+      <c r="L25">
+        <v>1.5285709999999999</v>
+      </c>
+      <c r="M25">
+        <v>21</v>
+      </c>
+      <c r="N25" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>105</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>60</v>
+      </c>
+      <c r="R25">
+        <v>321</v>
+      </c>
+      <c r="S25">
+        <v>327.10280399999999</v>
+      </c>
+      <c r="T25">
+        <v>5</v>
+      </c>
+      <c r="V25">
+        <v>21</v>
+      </c>
+      <c r="W25">
+        <v>1.5576319999999999</v>
+      </c>
+      <c r="X25">
+        <v>5</v>
+      </c>
+      <c r="Y25">
+        <v>1.5576319999999999</v>
+      </c>
+      <c r="Z25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26">
+        <v>36</v>
+      </c>
+      <c r="J26" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26">
+        <v>834</v>
+      </c>
+      <c r="L26">
+        <v>1.300959</v>
+      </c>
+      <c r="M26">
+        <v>27.972222219999999</v>
+      </c>
+      <c r="N26" t="s">
+        <v>29</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>1007</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>60</v>
+      </c>
+      <c r="R26">
+        <v>1085</v>
+      </c>
+      <c r="S26">
+        <v>928.11059899999998</v>
+      </c>
+      <c r="T26">
+        <v>36</v>
+      </c>
+      <c r="V26">
+        <v>27.972221999999999</v>
+      </c>
+      <c r="W26">
+        <v>3.3179720000000001</v>
+      </c>
+      <c r="X26">
+        <v>37</v>
+      </c>
+      <c r="Y26">
+        <v>3.4101379999999999</v>
+      </c>
+      <c r="Z26">
+        <v>27.216215999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" t="s">
+        <v>48</v>
+      </c>
+      <c r="H27" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27">
+        <v>47</v>
+      </c>
+      <c r="J27" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27">
+        <v>1562</v>
+      </c>
+      <c r="L27">
+        <v>1.1766970000000001</v>
+      </c>
+      <c r="M27">
+        <v>38.276595739999998</v>
+      </c>
+      <c r="N27" t="s">
+        <v>29</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>1799</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>60</v>
+      </c>
+      <c r="R27">
+        <v>1838</v>
+      </c>
+      <c r="S27">
+        <v>978.78128400000003</v>
+      </c>
+      <c r="T27">
+        <v>47</v>
+      </c>
+      <c r="V27">
+        <v>38.276595999999998</v>
+      </c>
+      <c r="W27">
+        <v>2.5571269999999999</v>
+      </c>
+      <c r="X27">
+        <v>53</v>
+      </c>
+      <c r="Y27">
+        <v>2.883569</v>
+      </c>
+      <c r="Z27">
+        <v>33.943396</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28">
+        <v>47</v>
+      </c>
+      <c r="J28" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28">
+        <v>1666</v>
+      </c>
+      <c r="L28">
+        <v>1.468788</v>
+      </c>
+      <c r="M28">
+        <v>35.276595739999998</v>
+      </c>
+      <c r="N28" t="s">
+        <v>29</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>1658</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>56</v>
+      </c>
+      <c r="R28">
+        <v>2447</v>
+      </c>
+      <c r="S28">
+        <v>677.56436499999995</v>
+      </c>
+      <c r="T28">
+        <v>47</v>
+      </c>
+      <c r="V28">
+        <v>35.276595999999998</v>
+      </c>
+      <c r="W28">
+        <v>1.9207190000000001</v>
+      </c>
+      <c r="X28">
+        <v>57</v>
+      </c>
+      <c r="Y28">
+        <v>2.329383</v>
+      </c>
+      <c r="Z28">
+        <v>29.087719</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" t="s">
+        <v>31</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="N29" t="s">
+        <v>29</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>56</v>
+      </c>
+      <c r="R29">
+        <v>1</v>
+      </c>
+      <c r="S29">
+        <v>2000</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" t="s">
+        <v>32</v>
+      </c>
+      <c r="H30" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30">
+        <v>5</v>
+      </c>
+      <c r="J30" t="s">
+        <v>30</v>
+      </c>
+      <c r="K30">
+        <v>387</v>
+      </c>
+      <c r="L30">
+        <v>1.2945739999999999</v>
+      </c>
+      <c r="M30">
+        <v>47.8</v>
+      </c>
+      <c r="N30" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>239</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>56</v>
+      </c>
+      <c r="R30">
+        <v>501</v>
+      </c>
+      <c r="S30">
+        <v>477.045908</v>
+      </c>
+      <c r="T30">
+        <v>5</v>
+      </c>
+      <c r="V30">
+        <v>47.8</v>
+      </c>
+      <c r="W30">
+        <v>0.998004</v>
+      </c>
+      <c r="X30">
+        <v>7</v>
+      </c>
+      <c r="Y30">
+        <v>1.3972059999999999</v>
+      </c>
+      <c r="Z30">
+        <v>34.142856999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" t="s">
+        <v>41</v>
+      </c>
+      <c r="F31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31">
+        <v>47</v>
+      </c>
+      <c r="L31">
+        <v>1.234043</v>
+      </c>
+      <c r="M31">
+        <v>17</v>
+      </c>
+      <c r="N31" t="s">
+        <v>29</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>17</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>56</v>
+      </c>
+      <c r="R31">
+        <v>58</v>
+      </c>
+      <c r="S31">
+        <v>293.10344800000001</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="V31">
+        <v>17</v>
+      </c>
+      <c r="W31">
+        <v>1.7241379999999999</v>
+      </c>
+      <c r="X31">
+        <v>1</v>
+      </c>
+      <c r="Y31">
+        <v>1.7241379999999999</v>
+      </c>
+      <c r="Z31">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" t="s">
+        <v>32</v>
+      </c>
+      <c r="H32" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32">
+        <v>29</v>
+      </c>
+      <c r="J32" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32">
+        <v>1016</v>
+      </c>
+      <c r="L32">
+        <v>1.401575</v>
+      </c>
+      <c r="M32">
+        <v>35.551724139999997</v>
+      </c>
+      <c r="N32" t="s">
+        <v>29</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>1031</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>56</v>
+      </c>
+      <c r="R32">
+        <v>1424</v>
+      </c>
+      <c r="S32">
+        <v>724.01685399999997</v>
+      </c>
+      <c r="T32">
+        <v>29</v>
+      </c>
+      <c r="V32">
+        <v>35.551724</v>
+      </c>
+      <c r="W32">
+        <v>2.0365169999999999</v>
+      </c>
+      <c r="X32">
+        <v>38</v>
+      </c>
+      <c r="Y32">
+        <v>2.668539</v>
+      </c>
+      <c r="Z32">
+        <v>27.131578999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33">
+        <v>70</v>
+      </c>
+      <c r="J33" t="s">
+        <v>30</v>
+      </c>
+      <c r="K33">
+        <v>1857</v>
+      </c>
+      <c r="L33">
+        <v>1.569736</v>
+      </c>
+      <c r="M33">
+        <v>37.5</v>
+      </c>
+      <c r="N33" t="s">
+        <v>29</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>2625</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>56</v>
+      </c>
+      <c r="R33">
+        <v>2915</v>
+      </c>
+      <c r="S33">
+        <v>900.51458000000002</v>
+      </c>
+      <c r="T33">
+        <v>70</v>
+      </c>
+      <c r="V33">
+        <v>37.5</v>
+      </c>
+      <c r="W33">
+        <v>2.4013719999999998</v>
+      </c>
+      <c r="X33">
+        <v>85</v>
+      </c>
+      <c r="Y33">
+        <v>2.9159519999999999</v>
+      </c>
+      <c r="Z33">
+        <v>30.882352999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34">
+        <v>44</v>
+      </c>
+      <c r="J34" t="s">
+        <v>30</v>
+      </c>
+      <c r="K34">
+        <v>1198</v>
+      </c>
+      <c r="L34">
+        <v>1.626878</v>
+      </c>
+      <c r="M34">
+        <v>25.886363639999999</v>
+      </c>
+      <c r="N34" t="s">
+        <v>29</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>1139</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>56</v>
+      </c>
+      <c r="R34">
+        <v>1949</v>
+      </c>
+      <c r="S34">
+        <v>584.40225799999996</v>
+      </c>
+      <c r="T34">
+        <v>44</v>
+      </c>
+      <c r="V34">
+        <v>25.886364</v>
+      </c>
+      <c r="W34">
+        <v>2.257568</v>
+      </c>
+      <c r="X34">
+        <v>55</v>
+      </c>
+      <c r="Y34">
+        <v>2.8219599999999998</v>
+      </c>
+      <c r="Z34">
+        <v>20.709091000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" t="s">
+        <v>46</v>
+      </c>
+      <c r="G35" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35">
+        <v>2</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="N35" t="s">
+        <v>29</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>2</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>56</v>
+      </c>
+      <c r="R35">
+        <v>2</v>
+      </c>
+      <c r="S35">
+        <v>1000</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H36" t="s">
+        <v>31</v>
+      </c>
+      <c r="I36">
+        <v>10</v>
+      </c>
+      <c r="J36" t="s">
+        <v>30</v>
+      </c>
+      <c r="K36">
+        <v>352</v>
+      </c>
+      <c r="L36">
+        <v>1.4602269999999999</v>
+      </c>
+      <c r="M36">
+        <v>21.8</v>
+      </c>
+      <c r="N36" t="s">
+        <v>29</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>218</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>56</v>
+      </c>
+      <c r="R36">
+        <v>514</v>
+      </c>
+      <c r="S36">
+        <v>424.12451399999998</v>
+      </c>
+      <c r="T36">
+        <v>10</v>
+      </c>
+      <c r="V36">
+        <v>21.8</v>
+      </c>
+      <c r="W36">
+        <v>1.9455249999999999</v>
+      </c>
+      <c r="X36">
+        <v>13</v>
+      </c>
+      <c r="Y36">
+        <v>2.5291830000000002</v>
+      </c>
+      <c r="Z36">
+        <v>16.769231000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" t="s">
+        <v>41</v>
+      </c>
+      <c r="F37" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" t="s">
+        <v>32</v>
+      </c>
+      <c r="H37" t="s">
+        <v>31</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37" t="s">
+        <v>30</v>
+      </c>
+      <c r="K37">
+        <v>91</v>
+      </c>
+      <c r="L37">
+        <v>1.373626</v>
+      </c>
+      <c r="M37">
+        <v>14</v>
+      </c>
+      <c r="N37" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
         <v>28</v>
       </c>
+      <c r="Q37" t="s">
+        <v>56</v>
+      </c>
+      <c r="R37">
+        <v>125</v>
+      </c>
+      <c r="S37">
+        <v>224</v>
+      </c>
+      <c r="T37">
+        <v>2</v>
+      </c>
+      <c r="V37">
+        <v>14</v>
+      </c>
+      <c r="W37">
+        <v>1.6</v>
+      </c>
+      <c r="X37">
+        <v>2</v>
+      </c>
+      <c r="Y37">
+        <v>1.6</v>
+      </c>
+      <c r="Z37">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38" t="s">
+        <v>31</v>
+      </c>
+      <c r="I38">
+        <v>32</v>
+      </c>
+      <c r="J38" t="s">
+        <v>30</v>
+      </c>
+      <c r="K38">
+        <v>931</v>
+      </c>
+      <c r="L38">
+        <v>1.43072</v>
+      </c>
+      <c r="M38">
+        <v>26.46875</v>
+      </c>
+      <c r="N38" t="s">
+        <v>29</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>847</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>56</v>
+      </c>
+      <c r="R38">
+        <v>1332</v>
+      </c>
+      <c r="S38">
+        <v>635.88588600000003</v>
+      </c>
+      <c r="T38">
+        <v>32</v>
+      </c>
+      <c r="V38">
+        <v>26.46875</v>
+      </c>
+      <c r="W38">
+        <v>2.4024019999999999</v>
+      </c>
+      <c r="X38">
+        <v>40</v>
+      </c>
+      <c r="Y38">
+        <v>3.0030030000000001</v>
+      </c>
+      <c r="Z38">
+        <v>21.175000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" t="s">
+        <v>34</v>
+      </c>
+      <c r="F39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39">
+        <v>131</v>
+      </c>
+      <c r="J39" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39">
+        <v>2088</v>
+      </c>
+      <c r="L39">
+        <v>1.6834290000000001</v>
+      </c>
+      <c r="M39">
+        <v>25.27480916</v>
+      </c>
+      <c r="N39" t="s">
+        <v>29</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>3311</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>56</v>
+      </c>
+      <c r="R39">
+        <v>3515</v>
+      </c>
+      <c r="S39">
+        <v>941.96301600000004</v>
+      </c>
+      <c r="T39">
+        <v>131</v>
+      </c>
+      <c r="V39">
+        <v>25.274809000000001</v>
+      </c>
+      <c r="W39">
+        <v>3.7268849999999998</v>
+      </c>
+      <c r="X39">
+        <v>157</v>
+      </c>
+      <c r="Y39">
+        <v>4.4665720000000002</v>
+      </c>
+      <c r="Z39">
+        <v>21.089172000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40">
+        <v>6</v>
+      </c>
+      <c r="J40" t="s">
+        <v>30</v>
+      </c>
+      <c r="K40">
+        <v>170</v>
+      </c>
+      <c r="L40">
+        <v>1.3117650000000001</v>
+      </c>
+      <c r="M40">
+        <v>28.166666670000001</v>
+      </c>
+      <c r="N40" t="s">
+        <v>29</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>169</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>56</v>
+      </c>
+      <c r="R40">
+        <v>223</v>
+      </c>
+      <c r="S40">
+        <v>757.847534</v>
+      </c>
+      <c r="T40">
+        <v>6</v>
+      </c>
+      <c r="V40">
+        <v>28.166667</v>
+      </c>
+      <c r="W40">
+        <v>2.6905830000000002</v>
+      </c>
+      <c r="X40">
+        <v>6</v>
+      </c>
+      <c r="Y40">
+        <v>2.6905830000000002</v>
+      </c>
+      <c r="Z40">
+        <v>28.166667</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" t="s">
+        <v>32</v>
+      </c>
+      <c r="H41" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41" t="s">
+        <v>30</v>
+      </c>
+      <c r="K41">
+        <v>59</v>
+      </c>
+      <c r="L41">
+        <v>1.457627</v>
+      </c>
+      <c r="M41">
+        <v>41</v>
+      </c>
+      <c r="N41" t="s">
+        <v>29</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>41</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>56</v>
+      </c>
+      <c r="R41">
+        <v>86</v>
+      </c>
+      <c r="S41">
+        <v>476.74418600000001</v>
+      </c>
+      <c r="T41">
+        <v>1</v>
+      </c>
+      <c r="V41">
+        <v>41</v>
+      </c>
+      <c r="W41">
+        <v>1.1627909999999999</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="Y41">
+        <v>1.1627909999999999</v>
+      </c>
+      <c r="Z41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" t="s">
+        <v>41</v>
+      </c>
+      <c r="F42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" t="s">
+        <v>32</v>
+      </c>
+      <c r="H42" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42" t="s">
+        <v>30</v>
+      </c>
+      <c r="K42">
+        <v>19</v>
+      </c>
+      <c r="L42">
+        <v>1.736842</v>
+      </c>
+      <c r="M42">
+        <v>6</v>
+      </c>
+      <c r="N42" t="s">
+        <v>29</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>6</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>56</v>
+      </c>
+      <c r="R42">
+        <v>33</v>
+      </c>
+      <c r="S42">
+        <v>181.81818200000001</v>
+      </c>
+      <c r="T42">
+        <v>1</v>
+      </c>
+      <c r="V42">
+        <v>6</v>
+      </c>
+      <c r="W42">
+        <v>3.030303</v>
+      </c>
+      <c r="X42">
+        <v>2</v>
+      </c>
+      <c r="Y42">
+        <v>6.0606059999999999</v>
+      </c>
+      <c r="Z42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" t="s">
+        <v>32</v>
+      </c>
+      <c r="H43" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43">
+        <v>5</v>
+      </c>
+      <c r="J43" t="s">
+        <v>30</v>
+      </c>
+      <c r="K43">
+        <v>192</v>
+      </c>
+      <c r="L43">
+        <v>1.3697919999999999</v>
+      </c>
+      <c r="M43">
+        <v>41.2</v>
+      </c>
+      <c r="N43" t="s">
+        <v>29</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>206</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>56</v>
+      </c>
+      <c r="R43">
+        <v>263</v>
+      </c>
+      <c r="S43">
+        <v>783.26996199999996</v>
+      </c>
+      <c r="T43">
+        <v>5</v>
+      </c>
+      <c r="V43">
+        <v>41.2</v>
+      </c>
+      <c r="W43">
+        <v>1.901141</v>
+      </c>
+      <c r="X43">
+        <v>5</v>
+      </c>
+      <c r="Y43">
+        <v>1.901141</v>
+      </c>
+      <c r="Z43">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" t="s">
+        <v>57</v>
+      </c>
+      <c r="D44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" t="s">
+        <v>34</v>
+      </c>
+      <c r="F44" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44" t="s">
+        <v>32</v>
+      </c>
+      <c r="H44" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44">
+        <v>232</v>
+      </c>
+      <c r="J44" t="s">
+        <v>30</v>
+      </c>
+      <c r="K44">
+        <v>3708</v>
+      </c>
+      <c r="L44">
+        <v>1.4161269999999999</v>
+      </c>
+      <c r="M44">
+        <v>23.142241380000002</v>
+      </c>
+      <c r="N44" t="s">
+        <v>29</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>5369</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>56</v>
+      </c>
+      <c r="R44">
+        <v>5251</v>
+      </c>
+      <c r="S44">
+        <v>1022.47191</v>
+      </c>
+      <c r="T44">
+        <v>232</v>
+      </c>
+      <c r="V44">
+        <v>23.142240999999999</v>
+      </c>
+      <c r="W44">
+        <v>4.4182059999999996</v>
+      </c>
+      <c r="X44">
+        <v>249</v>
+      </c>
+      <c r="Y44">
+        <v>4.7419539999999998</v>
+      </c>
+      <c r="Z44">
+        <v>21.562249000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" t="s">
+        <v>33</v>
+      </c>
+      <c r="G45" t="s">
+        <v>32</v>
+      </c>
+      <c r="H45" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45">
+        <v>78</v>
+      </c>
+      <c r="J45" t="s">
+        <v>30</v>
+      </c>
+      <c r="K45">
+        <v>1184</v>
+      </c>
+      <c r="L45">
+        <v>1.5371619999999999</v>
+      </c>
+      <c r="M45">
+        <v>25.705128210000002</v>
+      </c>
+      <c r="N45" t="s">
+        <v>29</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>2005</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>54</v>
+      </c>
+      <c r="R45">
+        <v>1820</v>
+      </c>
+      <c r="S45">
+        <v>1101.6483519999999</v>
+      </c>
+      <c r="T45">
+        <v>78</v>
+      </c>
+      <c r="V45">
+        <v>25.705127999999998</v>
+      </c>
+      <c r="W45">
+        <v>4.2857139999999996</v>
+      </c>
+      <c r="X45">
+        <v>86</v>
+      </c>
+      <c r="Y45">
+        <v>4.7252749999999999</v>
+      </c>
+      <c r="Z45">
+        <v>23.313953000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" t="s">
+        <v>43</v>
+      </c>
+      <c r="F46" t="s">
+        <v>46</v>
+      </c>
+      <c r="G46" t="s">
+        <v>32</v>
+      </c>
+      <c r="H46" t="s">
+        <v>31</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <v>9</v>
+      </c>
+      <c r="N46" t="s">
+        <v>29</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>4</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>54</v>
+      </c>
+      <c r="R46">
+        <v>9</v>
+      </c>
+      <c r="S46">
+        <v>444.44444399999998</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" t="s">
+        <v>55</v>
+      </c>
+      <c r="D47" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" t="s">
+        <v>33</v>
+      </c>
+      <c r="G47" t="s">
+        <v>32</v>
+      </c>
+      <c r="H47" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47">
+        <v>3</v>
+      </c>
+      <c r="J47" t="s">
+        <v>30</v>
+      </c>
+      <c r="K47">
+        <v>194</v>
+      </c>
+      <c r="L47">
+        <v>1.201031</v>
+      </c>
+      <c r="M47">
+        <v>41.333333330000002</v>
+      </c>
+      <c r="N47" t="s">
+        <v>29</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>124</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>54</v>
+      </c>
+      <c r="R47">
+        <v>233</v>
+      </c>
+      <c r="S47">
+        <v>532.18884100000002</v>
+      </c>
+      <c r="T47">
+        <v>3</v>
+      </c>
+      <c r="V47">
+        <v>41.333333000000003</v>
+      </c>
+      <c r="W47">
+        <v>1.2875540000000001</v>
+      </c>
+      <c r="X47">
+        <v>3</v>
+      </c>
+      <c r="Y47">
+        <v>1.2875540000000001</v>
+      </c>
+      <c r="Z47">
+        <v>41.333333000000003</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" t="s">
+        <v>37</v>
+      </c>
+      <c r="C48" t="s">
+        <v>55</v>
+      </c>
+      <c r="D48" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" t="s">
+        <v>41</v>
+      </c>
+      <c r="F48" t="s">
+        <v>33</v>
+      </c>
+      <c r="G48" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" t="s">
+        <v>31</v>
+      </c>
+      <c r="I48">
+        <v>3</v>
+      </c>
+      <c r="J48" t="s">
+        <v>30</v>
+      </c>
+      <c r="K48">
+        <v>102</v>
+      </c>
+      <c r="L48">
+        <v>1.3921570000000001</v>
+      </c>
+      <c r="M48">
+        <v>16</v>
+      </c>
+      <c r="N48" t="s">
+        <v>29</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>48</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>54</v>
+      </c>
+      <c r="R48">
+        <v>142</v>
+      </c>
+      <c r="S48">
+        <v>338.02816899999999</v>
+      </c>
+      <c r="T48">
+        <v>3</v>
+      </c>
+      <c r="V48">
+        <v>16</v>
+      </c>
+      <c r="W48">
+        <v>2.112676</v>
+      </c>
+      <c r="X48">
+        <v>3</v>
+      </c>
+      <c r="Y48">
+        <v>2.112676</v>
+      </c>
+      <c r="Z48">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" t="s">
+        <v>40</v>
+      </c>
+      <c r="F49" t="s">
+        <v>33</v>
+      </c>
+      <c r="G49" t="s">
+        <v>32</v>
+      </c>
+      <c r="H49" t="s">
+        <v>31</v>
+      </c>
+      <c r="I49">
+        <v>51</v>
+      </c>
+      <c r="J49" t="s">
+        <v>30</v>
+      </c>
+      <c r="K49">
+        <v>870</v>
+      </c>
+      <c r="L49">
+        <v>1.4229890000000001</v>
+      </c>
+      <c r="M49">
+        <v>29.39215686</v>
+      </c>
+      <c r="N49" t="s">
+        <v>29</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>1499</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>54</v>
+      </c>
+      <c r="R49">
+        <v>1238</v>
+      </c>
+      <c r="S49">
+        <v>1210.8239100000001</v>
+      </c>
+      <c r="T49">
+        <v>51</v>
+      </c>
+      <c r="V49">
+        <v>29.392157000000001</v>
+      </c>
+      <c r="W49">
+        <v>4.119548</v>
+      </c>
+      <c r="X49">
+        <v>63</v>
+      </c>
+      <c r="Y49">
+        <v>5.0888530000000003</v>
+      </c>
+      <c r="Z49">
+        <v>23.793651000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" t="s">
+        <v>34</v>
+      </c>
+      <c r="F50" t="s">
+        <v>33</v>
+      </c>
+      <c r="G50" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" t="s">
+        <v>31</v>
+      </c>
+      <c r="I50">
+        <v>68</v>
+      </c>
+      <c r="J50" t="s">
+        <v>30</v>
+      </c>
+      <c r="K50">
+        <v>1028</v>
+      </c>
+      <c r="L50">
+        <v>1.3599220000000001</v>
+      </c>
+      <c r="M50">
+        <v>34.382352939999997</v>
+      </c>
+      <c r="N50" t="s">
+        <v>29</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>2338</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>54</v>
+      </c>
+      <c r="R50">
+        <v>1398</v>
+      </c>
+      <c r="S50">
+        <v>1672.3891269999999</v>
+      </c>
+      <c r="T50">
+        <v>68</v>
+      </c>
+      <c r="V50">
+        <v>34.382353000000002</v>
+      </c>
+      <c r="W50">
+        <v>4.8640920000000003</v>
+      </c>
+      <c r="X50">
+        <v>72</v>
+      </c>
+      <c r="Y50">
+        <v>5.1502150000000002</v>
+      </c>
+      <c r="Z50">
+        <v>32.472222000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" t="s">
+        <v>55</v>
+      </c>
+      <c r="D51" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" t="s">
+        <v>34</v>
+      </c>
+      <c r="F51" t="s">
+        <v>46</v>
+      </c>
+      <c r="G51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H51" t="s">
+        <v>31</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51">
+        <v>2</v>
+      </c>
+      <c r="N51" t="s">
+        <v>29</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>5</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>54</v>
+      </c>
+      <c r="R51">
+        <v>2</v>
+      </c>
+      <c r="S51">
+        <v>2500</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52" t="s">
+        <v>53</v>
+      </c>
+      <c r="D52" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" t="s">
+        <v>43</v>
+      </c>
+      <c r="F52" t="s">
+        <v>33</v>
+      </c>
+      <c r="G52" t="s">
+        <v>48</v>
+      </c>
+      <c r="H52" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52">
+        <v>6</v>
+      </c>
+      <c r="J52" t="s">
+        <v>30</v>
+      </c>
+      <c r="K52">
+        <v>146</v>
+      </c>
+      <c r="L52">
+        <v>1.3150679999999999</v>
+      </c>
+      <c r="M52">
+        <v>53.5</v>
+      </c>
+      <c r="N52" t="s">
+        <v>29</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>321</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>51</v>
+      </c>
+      <c r="R52">
+        <v>192</v>
+      </c>
+      <c r="S52">
+        <v>1671.875</v>
+      </c>
+      <c r="T52">
+        <v>6</v>
+      </c>
+      <c r="V52">
+        <v>53.5</v>
+      </c>
+      <c r="W52">
+        <v>3.125</v>
+      </c>
+      <c r="X52">
+        <v>6</v>
+      </c>
+      <c r="Y52">
+        <v>3.125</v>
+      </c>
+      <c r="Z52">
+        <v>53.5</v>
+      </c>
+      <c r="AA52">
+        <v>3</v>
+      </c>
+      <c r="AB52">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" t="s">
+        <v>53</v>
+      </c>
+      <c r="D53" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G53" t="s">
+        <v>48</v>
+      </c>
+      <c r="H53" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53" t="s">
+        <v>30</v>
+      </c>
+      <c r="K53">
+        <v>120</v>
+      </c>
+      <c r="L53">
+        <v>1.2083330000000001</v>
+      </c>
+      <c r="M53">
+        <v>92</v>
+      </c>
+      <c r="N53" t="s">
+        <v>29</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>92</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>51</v>
+      </c>
+      <c r="R53">
+        <v>145</v>
+      </c>
+      <c r="S53">
+        <v>634.48275899999999</v>
+      </c>
+      <c r="T53">
+        <v>1</v>
+      </c>
+      <c r="V53">
+        <v>92</v>
+      </c>
+      <c r="W53">
+        <v>0.68965500000000002</v>
+      </c>
+      <c r="X53">
+        <v>1</v>
+      </c>
+      <c r="Y53">
+        <v>0.68965500000000002</v>
+      </c>
+      <c r="Z53">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" t="s">
+        <v>41</v>
+      </c>
+      <c r="F54" t="s">
+        <v>33</v>
+      </c>
+      <c r="G54" t="s">
+        <v>48</v>
+      </c>
+      <c r="H54" t="s">
+        <v>31</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54" t="s">
+        <v>30</v>
+      </c>
+      <c r="K54">
+        <v>15</v>
+      </c>
+      <c r="L54">
+        <v>1.1333329999999999</v>
+      </c>
+      <c r="M54">
+        <v>9</v>
+      </c>
+      <c r="N54" t="s">
+        <v>29</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>9</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>51</v>
+      </c>
+      <c r="R54">
+        <v>17</v>
+      </c>
+      <c r="S54">
+        <v>529.41176499999995</v>
+      </c>
+      <c r="T54">
+        <v>1</v>
+      </c>
+      <c r="V54">
+        <v>9</v>
+      </c>
+      <c r="W54">
+        <v>5.8823530000000002</v>
+      </c>
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Y54">
+        <v>5.8823530000000002</v>
+      </c>
+      <c r="Z54">
+        <v>9</v>
+      </c>
+      <c r="AA54">
+        <v>1</v>
+      </c>
+      <c r="AB54">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" t="s">
+        <v>37</v>
+      </c>
+      <c r="C55" t="s">
+        <v>53</v>
+      </c>
+      <c r="D55" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" t="s">
+        <v>40</v>
+      </c>
+      <c r="F55" t="s">
+        <v>33</v>
+      </c>
+      <c r="G55" t="s">
+        <v>48</v>
+      </c>
+      <c r="H55" t="s">
+        <v>31</v>
+      </c>
+      <c r="I55">
+        <v>5</v>
+      </c>
+      <c r="J55" t="s">
+        <v>30</v>
+      </c>
+      <c r="K55">
+        <v>285</v>
+      </c>
+      <c r="L55">
+        <v>1.22807</v>
+      </c>
+      <c r="M55">
+        <v>64.8</v>
+      </c>
+      <c r="N55" t="s">
+        <v>29</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>324</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>51</v>
+      </c>
+      <c r="R55">
+        <v>350</v>
+      </c>
+      <c r="S55">
+        <v>925.71428600000002</v>
+      </c>
+      <c r="T55">
+        <v>5</v>
+      </c>
+      <c r="V55">
+        <v>64.8</v>
+      </c>
+      <c r="W55">
+        <v>1.428571</v>
+      </c>
+      <c r="X55">
+        <v>5</v>
+      </c>
+      <c r="Y55">
+        <v>1.428571</v>
+      </c>
+      <c r="Z55">
+        <v>64.8</v>
+      </c>
+      <c r="AA55">
+        <v>2</v>
+      </c>
+      <c r="AB55">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" t="s">
+        <v>37</v>
+      </c>
+      <c r="C56" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" t="s">
+        <v>34</v>
+      </c>
+      <c r="F56" t="s">
+        <v>33</v>
+      </c>
+      <c r="G56" t="s">
+        <v>48</v>
+      </c>
+      <c r="H56" t="s">
+        <v>31</v>
+      </c>
+      <c r="I56">
+        <v>112</v>
+      </c>
+      <c r="J56" t="s">
+        <v>30</v>
+      </c>
+      <c r="K56">
+        <v>4324</v>
+      </c>
+      <c r="L56">
+        <v>1.307817</v>
+      </c>
+      <c r="M56">
+        <v>50.428571429999998</v>
+      </c>
+      <c r="N56" t="s">
+        <v>29</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>5648</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>51</v>
+      </c>
+      <c r="R56">
+        <v>5655</v>
+      </c>
+      <c r="S56">
+        <v>998.762157</v>
+      </c>
+      <c r="T56">
+        <v>112</v>
+      </c>
+      <c r="V56">
+        <v>50.428570999999998</v>
+      </c>
+      <c r="W56">
+        <v>1.980548</v>
+      </c>
+      <c r="X56">
+        <v>117</v>
+      </c>
+      <c r="Y56">
+        <v>2.0689660000000001</v>
+      </c>
+      <c r="Z56">
+        <v>48.273504000000003</v>
+      </c>
+      <c r="AA56">
+        <v>57</v>
+      </c>
+      <c r="AB56">
+        <v>99.087719000000007</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" t="s">
+        <v>43</v>
+      </c>
+      <c r="F57" t="s">
+        <v>33</v>
+      </c>
+      <c r="G57" t="s">
+        <v>48</v>
+      </c>
+      <c r="H57" t="s">
+        <v>31</v>
+      </c>
+      <c r="I57">
+        <v>30</v>
+      </c>
+      <c r="J57" t="s">
+        <v>30</v>
+      </c>
+      <c r="K57">
+        <v>1000</v>
+      </c>
+      <c r="L57">
+        <v>1.6870000000000001</v>
+      </c>
+      <c r="M57">
+        <v>48.466666670000002</v>
+      </c>
+      <c r="N57" t="s">
+        <v>29</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>1454</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>51</v>
+      </c>
+      <c r="R57">
+        <v>1687</v>
+      </c>
+      <c r="S57">
+        <v>861.88500299999998</v>
+      </c>
+      <c r="T57">
+        <v>30</v>
+      </c>
+      <c r="V57">
+        <v>48.466667000000001</v>
+      </c>
+      <c r="W57">
+        <v>1.778305</v>
+      </c>
+      <c r="X57">
+        <v>36</v>
+      </c>
+      <c r="Y57">
+        <v>2.133966</v>
+      </c>
+      <c r="Z57">
+        <v>40.388888999999999</v>
+      </c>
+      <c r="AA57">
+        <v>28</v>
+      </c>
+      <c r="AB57">
+        <v>51.928570999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58" t="s">
+        <v>37</v>
+      </c>
+      <c r="C58" t="s">
+        <v>52</v>
+      </c>
+      <c r="D58" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" t="s">
+        <v>43</v>
+      </c>
+      <c r="F58" t="s">
+        <v>46</v>
+      </c>
+      <c r="G58" t="s">
+        <v>48</v>
+      </c>
+      <c r="H58" t="s">
+        <v>31</v>
+      </c>
+      <c r="K58">
+        <v>1</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="N58" t="s">
+        <v>29</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>51</v>
+      </c>
+      <c r="R58">
+        <v>1</v>
+      </c>
+      <c r="S58">
+        <v>1000</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" t="s">
+        <v>37</v>
+      </c>
+      <c r="C59" t="s">
+        <v>52</v>
+      </c>
+      <c r="D59" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" t="s">
+        <v>33</v>
+      </c>
+      <c r="G59" t="s">
+        <v>48</v>
+      </c>
+      <c r="H59" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59">
+        <v>3</v>
+      </c>
+      <c r="J59" t="s">
+        <v>30</v>
+      </c>
+      <c r="K59">
+        <v>233</v>
+      </c>
+      <c r="L59">
+        <v>1.416309</v>
+      </c>
+      <c r="M59">
+        <v>58</v>
+      </c>
+      <c r="N59" t="s">
+        <v>29</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>174</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>51</v>
+      </c>
+      <c r="R59">
+        <v>330</v>
+      </c>
+      <c r="S59">
+        <v>527.27272700000003</v>
+      </c>
+      <c r="T59">
+        <v>3</v>
+      </c>
+      <c r="V59">
+        <v>58</v>
+      </c>
+      <c r="W59">
+        <v>0.90909099999999998</v>
+      </c>
+      <c r="X59">
+        <v>3</v>
+      </c>
+      <c r="Y59">
+        <v>0.90909099999999998</v>
+      </c>
+      <c r="Z59">
+        <v>58</v>
+      </c>
+      <c r="AA59">
+        <v>2</v>
+      </c>
+      <c r="AB59">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" t="s">
+        <v>52</v>
+      </c>
+      <c r="D60" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" t="s">
+        <v>41</v>
+      </c>
+      <c r="F60" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60" t="s">
+        <v>48</v>
+      </c>
+      <c r="H60" t="s">
+        <v>31</v>
+      </c>
+      <c r="K60">
+        <v>103</v>
+      </c>
+      <c r="L60">
+        <v>1.3398060000000001</v>
+      </c>
+      <c r="N60" t="s">
+        <v>29</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>31</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>51</v>
+      </c>
+      <c r="R60">
+        <v>138</v>
+      </c>
+      <c r="S60">
+        <v>224.63768099999999</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" t="s">
+        <v>37</v>
+      </c>
+      <c r="C61" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" t="s">
+        <v>40</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" t="s">
+        <v>48</v>
+      </c>
+      <c r="H61" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61">
+        <v>8</v>
+      </c>
+      <c r="J61" t="s">
+        <v>30</v>
+      </c>
+      <c r="K61">
+        <v>371</v>
+      </c>
+      <c r="L61">
+        <v>1.382749</v>
+      </c>
+      <c r="M61">
+        <v>49</v>
+      </c>
+      <c r="N61" t="s">
+        <v>29</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>392</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>51</v>
+      </c>
+      <c r="R61">
+        <v>513</v>
+      </c>
+      <c r="S61">
+        <v>764.13255400000003</v>
+      </c>
+      <c r="T61">
+        <v>8</v>
+      </c>
+      <c r="V61">
+        <v>49</v>
+      </c>
+      <c r="W61">
+        <v>1.5594539999999999</v>
+      </c>
+      <c r="X61">
+        <v>9</v>
+      </c>
+      <c r="Y61">
+        <v>1.754386</v>
+      </c>
+      <c r="Z61">
+        <v>43.555556000000003</v>
+      </c>
+      <c r="AA61">
+        <v>6</v>
+      </c>
+      <c r="AB61">
+        <v>65.333332999999996</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62" t="s">
+        <v>33</v>
+      </c>
+      <c r="G62" t="s">
+        <v>48</v>
+      </c>
+      <c r="H62" t="s">
+        <v>31</v>
+      </c>
+      <c r="I62">
+        <v>87</v>
+      </c>
+      <c r="J62" t="s">
+        <v>30</v>
+      </c>
+      <c r="K62">
+        <v>2255</v>
+      </c>
+      <c r="L62">
+        <v>1.5019960000000001</v>
+      </c>
+      <c r="M62">
+        <v>41.367816089999998</v>
+      </c>
+      <c r="N62" t="s">
+        <v>29</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>3599</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>51</v>
+      </c>
+      <c r="R62">
+        <v>3387</v>
+      </c>
+      <c r="S62">
+        <v>1062.592265</v>
+      </c>
+      <c r="T62">
+        <v>87</v>
+      </c>
+      <c r="V62">
+        <v>41.367815999999998</v>
+      </c>
+      <c r="W62">
+        <v>2.5686450000000001</v>
+      </c>
+      <c r="X62">
+        <v>104</v>
+      </c>
+      <c r="Y62">
+        <v>3.0705640000000001</v>
+      </c>
+      <c r="Z62">
+        <v>34.605769000000002</v>
+      </c>
+      <c r="AA62">
+        <v>71</v>
+      </c>
+      <c r="AB62">
+        <v>50.690140999999997</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63" t="s">
+        <v>50</v>
+      </c>
+      <c r="D63" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" t="s">
+        <v>43</v>
+      </c>
+      <c r="F63" t="s">
+        <v>33</v>
+      </c>
+      <c r="G63" t="s">
+        <v>32</v>
+      </c>
+      <c r="H63" t="s">
+        <v>31</v>
+      </c>
+      <c r="I63">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s">
+        <v>30</v>
+      </c>
+      <c r="K63">
+        <v>783</v>
+      </c>
+      <c r="L63">
+        <v>1.3116220000000001</v>
+      </c>
+      <c r="M63">
+        <v>43.714285709999999</v>
+      </c>
+      <c r="N63" t="s">
+        <v>29</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>918</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>44</v>
+      </c>
+      <c r="R63">
+        <v>1027</v>
+      </c>
+      <c r="S63">
+        <v>893.86562800000002</v>
+      </c>
+      <c r="T63">
+        <v>21</v>
+      </c>
+      <c r="V63">
+        <v>43.714286000000001</v>
+      </c>
+      <c r="W63">
+        <v>2.044791</v>
+      </c>
+      <c r="X63">
+        <v>28</v>
+      </c>
+      <c r="Y63">
+        <v>2.726388</v>
+      </c>
+      <c r="Z63">
+        <v>32.785713999999999</v>
+      </c>
+      <c r="AA63">
+        <v>19</v>
+      </c>
+      <c r="AB63">
+        <v>48.315789000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" t="s">
+        <v>37</v>
+      </c>
+      <c r="C64" t="s">
+        <v>50</v>
+      </c>
+      <c r="D64" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" t="s">
+        <v>43</v>
+      </c>
+      <c r="F64" t="s">
+        <v>46</v>
+      </c>
+      <c r="G64" t="s">
+        <v>32</v>
+      </c>
+      <c r="H64" t="s">
+        <v>31</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="N64" t="s">
+        <v>29</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>44</v>
+      </c>
+      <c r="R64">
+        <v>1</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65" t="s">
+        <v>50</v>
+      </c>
+      <c r="D65" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" t="s">
+        <v>42</v>
+      </c>
+      <c r="F65" t="s">
+        <v>33</v>
+      </c>
+      <c r="G65" t="s">
+        <v>32</v>
+      </c>
+      <c r="H65" t="s">
+        <v>31</v>
+      </c>
+      <c r="I65">
+        <v>6</v>
+      </c>
+      <c r="J65" t="s">
+        <v>30</v>
+      </c>
+      <c r="K65">
+        <v>251</v>
+      </c>
+      <c r="L65">
+        <v>1.3147409999999999</v>
+      </c>
+      <c r="M65">
+        <v>22.833333329999999</v>
+      </c>
+      <c r="N65" t="s">
+        <v>29</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>137</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>44</v>
+      </c>
+      <c r="R65">
+        <v>330</v>
+      </c>
+      <c r="S65">
+        <v>415.15151500000002</v>
+      </c>
+      <c r="T65">
+        <v>6</v>
+      </c>
+      <c r="V65">
+        <v>22.833333</v>
+      </c>
+      <c r="W65">
+        <v>1.818182</v>
+      </c>
+      <c r="X65">
+        <v>8</v>
+      </c>
+      <c r="Y65">
+        <v>2.424242</v>
+      </c>
+      <c r="Z65">
+        <v>17.125</v>
+      </c>
+      <c r="AA65">
+        <v>5</v>
+      </c>
+      <c r="AB65">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" t="s">
+        <v>37</v>
+      </c>
+      <c r="C66" t="s">
+        <v>50</v>
+      </c>
+      <c r="D66" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" t="s">
+        <v>41</v>
+      </c>
+      <c r="F66" t="s">
+        <v>33</v>
+      </c>
+      <c r="G66" t="s">
+        <v>32</v>
+      </c>
+      <c r="H66" t="s">
+        <v>31</v>
+      </c>
+      <c r="K66">
+        <v>83</v>
+      </c>
+      <c r="L66">
+        <v>1.2048190000000001</v>
+      </c>
+      <c r="N66" t="s">
+        <v>29</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>22</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>44</v>
+      </c>
+      <c r="R66">
+        <v>100</v>
+      </c>
+      <c r="S66">
+        <v>220</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" t="s">
+        <v>37</v>
+      </c>
+      <c r="C67" t="s">
+        <v>50</v>
+      </c>
+      <c r="D67" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" t="s">
+        <v>40</v>
+      </c>
+      <c r="F67" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" t="s">
+        <v>32</v>
+      </c>
+      <c r="H67" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67">
+        <v>19</v>
+      </c>
+      <c r="J67" t="s">
+        <v>30</v>
+      </c>
+      <c r="K67">
+        <v>524</v>
+      </c>
+      <c r="L67">
+        <v>1.2748090000000001</v>
+      </c>
+      <c r="M67">
+        <v>29.05263158</v>
+      </c>
+      <c r="N67" t="s">
+        <v>29</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>552</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>44</v>
+      </c>
+      <c r="R67">
+        <v>668</v>
+      </c>
+      <c r="S67">
+        <v>826.34730500000001</v>
+      </c>
+      <c r="T67">
+        <v>19</v>
+      </c>
+      <c r="V67">
+        <v>29.052631999999999</v>
+      </c>
+      <c r="W67">
+        <v>2.8443109999999998</v>
+      </c>
+      <c r="X67">
+        <v>21</v>
+      </c>
+      <c r="Y67">
+        <v>3.143713</v>
+      </c>
+      <c r="Z67">
+        <v>26.285713999999999</v>
+      </c>
+      <c r="AA67">
+        <v>17</v>
+      </c>
+      <c r="AB67">
+        <v>32.470587999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" t="s">
+        <v>37</v>
+      </c>
+      <c r="C68" t="s">
+        <v>50</v>
+      </c>
+      <c r="D68" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" t="s">
+        <v>34</v>
+      </c>
+      <c r="F68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G68" t="s">
+        <v>32</v>
+      </c>
+      <c r="H68" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68">
+        <v>110</v>
+      </c>
+      <c r="J68" t="s">
+        <v>30</v>
+      </c>
+      <c r="K68">
+        <v>2373</v>
+      </c>
+      <c r="L68">
+        <v>1.3919090000000001</v>
+      </c>
+      <c r="M68">
+        <v>32.127272730000001</v>
+      </c>
+      <c r="N68" t="s">
+        <v>29</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>3534</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>44</v>
+      </c>
+      <c r="R68">
+        <v>3303</v>
+      </c>
+      <c r="S68">
+        <v>1069.9364210000001</v>
+      </c>
+      <c r="T68">
+        <v>110</v>
+      </c>
+      <c r="V68">
+        <v>32.127273000000002</v>
+      </c>
+      <c r="W68">
+        <v>3.3303060000000002</v>
+      </c>
+      <c r="X68">
+        <v>137</v>
+      </c>
+      <c r="Y68">
+        <v>4.1477440000000003</v>
+      </c>
+      <c r="Z68">
+        <v>25.79562</v>
+      </c>
+      <c r="AA68">
+        <v>81</v>
+      </c>
+      <c r="AB68">
+        <v>43.629629999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>38</v>
+      </c>
+      <c r="B69" t="s">
+        <v>37</v>
+      </c>
+      <c r="C69" t="s">
+        <v>50</v>
+      </c>
+      <c r="D69" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" t="s">
+        <v>34</v>
+      </c>
+      <c r="F69" t="s">
+        <v>46</v>
+      </c>
+      <c r="G69" t="s">
+        <v>32</v>
+      </c>
+      <c r="H69" t="s">
+        <v>31</v>
+      </c>
+      <c r="K69">
+        <v>3</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="N69" t="s">
+        <v>29</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>3</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>44</v>
+      </c>
+      <c r="R69">
+        <v>3</v>
+      </c>
+      <c r="S69">
+        <v>1000</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>38</v>
+      </c>
+      <c r="B70" t="s">
+        <v>37</v>
+      </c>
+      <c r="C70" t="s">
+        <v>49</v>
+      </c>
+      <c r="D70" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" t="s">
+        <v>43</v>
+      </c>
+      <c r="F70" t="s">
+        <v>33</v>
+      </c>
+      <c r="G70" t="s">
+        <v>48</v>
+      </c>
+      <c r="H70" t="s">
+        <v>31</v>
+      </c>
+      <c r="I70">
+        <v>48</v>
+      </c>
+      <c r="J70" t="s">
+        <v>30</v>
+      </c>
+      <c r="K70">
+        <v>1394</v>
+      </c>
+      <c r="L70">
+        <v>1.366571</v>
+      </c>
+      <c r="M70">
+        <v>24.895833329999999</v>
+      </c>
+      <c r="N70" t="s">
+        <v>29</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>1195</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>47</v>
+      </c>
+      <c r="R70">
+        <v>1905</v>
+      </c>
+      <c r="S70">
+        <v>627.29658800000004</v>
+      </c>
+      <c r="T70">
+        <v>48</v>
+      </c>
+      <c r="V70">
+        <v>24.895833</v>
+      </c>
+      <c r="W70">
+        <v>2.519685</v>
+      </c>
+      <c r="X70">
+        <v>63</v>
+      </c>
+      <c r="Y70">
+        <v>3.3070870000000001</v>
+      </c>
+      <c r="Z70">
+        <v>18.968254000000002</v>
+      </c>
+      <c r="AA70">
+        <v>44</v>
+      </c>
+      <c r="AB70">
+        <v>27.159091</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" t="s">
+        <v>37</v>
+      </c>
+      <c r="C71" t="s">
+        <v>49</v>
+      </c>
+      <c r="D71" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" t="s">
+        <v>43</v>
+      </c>
+      <c r="F71" t="s">
+        <v>46</v>
+      </c>
+      <c r="G71" t="s">
+        <v>48</v>
+      </c>
+      <c r="H71" t="s">
+        <v>31</v>
+      </c>
+      <c r="K71">
+        <v>3</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="N71" t="s">
+        <v>29</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>47</v>
+      </c>
+      <c r="R71">
+        <v>3</v>
+      </c>
+      <c r="S71">
+        <v>333.33333299999998</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>38</v>
+      </c>
+      <c r="B72" t="s">
+        <v>37</v>
+      </c>
+      <c r="C72" t="s">
+        <v>49</v>
+      </c>
+      <c r="D72" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" t="s">
+        <v>42</v>
+      </c>
+      <c r="F72" t="s">
+        <v>33</v>
+      </c>
+      <c r="G72" t="s">
+        <v>48</v>
+      </c>
+      <c r="H72" t="s">
+        <v>31</v>
+      </c>
+      <c r="I72">
+        <v>9</v>
+      </c>
+      <c r="J72" t="s">
+        <v>30</v>
+      </c>
+      <c r="K72">
+        <v>336</v>
+      </c>
+      <c r="L72">
+        <v>1.321429</v>
+      </c>
+      <c r="M72">
+        <v>22.222222219999999</v>
+      </c>
+      <c r="N72" t="s">
+        <v>29</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>200</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>47</v>
+      </c>
+      <c r="R72">
+        <v>444</v>
+      </c>
+      <c r="S72">
+        <v>450.45044999999999</v>
+      </c>
+      <c r="T72">
+        <v>9</v>
+      </c>
+      <c r="V72">
+        <v>22.222221999999999</v>
+      </c>
+      <c r="W72">
+        <v>2.0270269999999999</v>
+      </c>
+      <c r="X72">
+        <v>10</v>
+      </c>
+      <c r="Y72">
+        <v>2.2522519999999999</v>
+      </c>
+      <c r="Z72">
+        <v>20</v>
+      </c>
+      <c r="AA72">
+        <v>9</v>
+      </c>
+      <c r="AB72">
+        <v>22.222221999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" t="s">
+        <v>37</v>
+      </c>
+      <c r="C73" t="s">
+        <v>49</v>
+      </c>
+      <c r="D73" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" t="s">
+        <v>41</v>
+      </c>
+      <c r="F73" t="s">
+        <v>33</v>
+      </c>
+      <c r="G73" t="s">
+        <v>48</v>
+      </c>
+      <c r="H73" t="s">
+        <v>31</v>
+      </c>
+      <c r="K73">
+        <v>62</v>
+      </c>
+      <c r="L73">
+        <v>1.274194</v>
+      </c>
+      <c r="N73" t="s">
+        <v>29</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>13</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>47</v>
+      </c>
+      <c r="R73">
+        <v>79</v>
+      </c>
+      <c r="S73">
+        <v>164.556962</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" t="s">
+        <v>37</v>
+      </c>
+      <c r="C74" t="s">
+        <v>49</v>
+      </c>
+      <c r="D74" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" t="s">
+        <v>40</v>
+      </c>
+      <c r="F74" t="s">
+        <v>33</v>
+      </c>
+      <c r="G74" t="s">
+        <v>48</v>
+      </c>
+      <c r="H74" t="s">
+        <v>31</v>
+      </c>
+      <c r="I74">
+        <v>36</v>
+      </c>
+      <c r="J74" t="s">
+        <v>30</v>
+      </c>
+      <c r="K74">
+        <v>1023</v>
+      </c>
+      <c r="L74">
+        <v>1.3196479999999999</v>
+      </c>
+      <c r="M74">
+        <v>22.333333329999999</v>
+      </c>
+      <c r="N74" t="s">
+        <v>29</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>804</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>47</v>
+      </c>
+      <c r="R74">
+        <v>1350</v>
+      </c>
+      <c r="S74">
+        <v>595.55555600000002</v>
+      </c>
+      <c r="T74">
+        <v>36</v>
+      </c>
+      <c r="V74">
+        <v>22.333333</v>
+      </c>
+      <c r="W74">
+        <v>2.6666669999999999</v>
+      </c>
+      <c r="X74">
+        <v>42</v>
+      </c>
+      <c r="Y74">
+        <v>3.1111110000000002</v>
+      </c>
+      <c r="Z74">
+        <v>19.142856999999999</v>
+      </c>
+      <c r="AA74">
+        <v>31</v>
+      </c>
+      <c r="AB74">
+        <v>25.935483999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" t="s">
+        <v>37</v>
+      </c>
+      <c r="C75" t="s">
+        <v>49</v>
+      </c>
+      <c r="D75" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" t="s">
+        <v>34</v>
+      </c>
+      <c r="F75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G75" t="s">
+        <v>48</v>
+      </c>
+      <c r="H75" t="s">
+        <v>31</v>
+      </c>
+      <c r="I75">
+        <v>114</v>
+      </c>
+      <c r="J75" t="s">
+        <v>30</v>
+      </c>
+      <c r="K75">
+        <v>2411</v>
+      </c>
+      <c r="L75">
+        <v>1.479884</v>
+      </c>
+      <c r="M75">
+        <v>26.219298250000001</v>
+      </c>
+      <c r="N75" t="s">
+        <v>29</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>2989</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>47</v>
+      </c>
+      <c r="R75">
+        <v>3568</v>
+      </c>
+      <c r="S75">
+        <v>837.72421499999996</v>
+      </c>
+      <c r="T75">
+        <v>114</v>
+      </c>
+      <c r="V75">
+        <v>26.219297999999998</v>
+      </c>
+      <c r="W75">
+        <v>3.1950669999999999</v>
+      </c>
+      <c r="X75">
+        <v>145</v>
+      </c>
+      <c r="Y75">
+        <v>4.0639010000000004</v>
+      </c>
+      <c r="Z75">
+        <v>20.613793000000001</v>
+      </c>
+      <c r="AA75">
+        <v>92</v>
+      </c>
+      <c r="AB75">
+        <v>32.489130000000003</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>38</v>
+      </c>
+      <c r="B76" t="s">
+        <v>37</v>
+      </c>
+      <c r="C76" t="s">
+        <v>49</v>
+      </c>
+      <c r="D76" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" t="s">
+        <v>34</v>
+      </c>
+      <c r="F76" t="s">
+        <v>46</v>
+      </c>
+      <c r="G76" t="s">
+        <v>48</v>
+      </c>
+      <c r="H76" t="s">
+        <v>31</v>
+      </c>
+      <c r="K76">
+        <v>2</v>
+      </c>
+      <c r="L76">
+        <v>1.5</v>
+      </c>
+      <c r="N76" t="s">
+        <v>29</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>2</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>47</v>
+      </c>
+      <c r="R76">
+        <v>3</v>
+      </c>
+      <c r="S76">
+        <v>666.66666699999996</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>38</v>
+      </c>
+      <c r="B77" t="s">
+        <v>37</v>
+      </c>
+      <c r="C77" t="s">
+        <v>45</v>
+      </c>
+      <c r="D77" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" t="s">
+        <v>43</v>
+      </c>
+      <c r="F77" t="s">
+        <v>33</v>
+      </c>
+      <c r="G77" t="s">
+        <v>32</v>
+      </c>
+      <c r="H77" t="s">
+        <v>31</v>
+      </c>
+      <c r="I77">
+        <v>4</v>
+      </c>
+      <c r="J77" t="s">
+        <v>30</v>
+      </c>
+      <c r="K77">
+        <v>141</v>
+      </c>
+      <c r="L77">
+        <v>1.2624109999999999</v>
+      </c>
+      <c r="M77">
+        <v>63</v>
+      </c>
+      <c r="N77" t="s">
+        <v>29</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>252</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>44</v>
+      </c>
+      <c r="R77">
+        <v>178</v>
+      </c>
+      <c r="S77">
+        <v>1415.730337</v>
+      </c>
+      <c r="T77">
+        <v>4</v>
+      </c>
+      <c r="V77">
+        <v>63</v>
+      </c>
+      <c r="W77">
+        <v>2.2471909999999999</v>
+      </c>
+      <c r="X77">
+        <v>10</v>
+      </c>
+      <c r="Y77">
+        <v>5.6179779999999999</v>
+      </c>
+      <c r="Z77">
+        <v>25.2</v>
+      </c>
+      <c r="AA77">
+        <v>3</v>
+      </c>
+      <c r="AB77">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" t="s">
+        <v>37</v>
+      </c>
+      <c r="C78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D78" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" t="s">
+        <v>43</v>
+      </c>
+      <c r="F78" t="s">
+        <v>46</v>
+      </c>
+      <c r="G78" t="s">
+        <v>32</v>
+      </c>
+      <c r="H78" t="s">
+        <v>31</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="N78" t="s">
+        <v>29</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>44</v>
+      </c>
+      <c r="R78">
+        <v>1</v>
+      </c>
+      <c r="S78">
+        <v>1000</v>
+      </c>
+      <c r="X78">
+        <v>0</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>38</v>
+      </c>
+      <c r="B79" t="s">
+        <v>37</v>
+      </c>
+      <c r="C79" t="s">
+        <v>45</v>
+      </c>
+      <c r="D79" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" t="s">
+        <v>42</v>
+      </c>
+      <c r="F79" t="s">
+        <v>33</v>
+      </c>
+      <c r="G79" t="s">
+        <v>32</v>
+      </c>
+      <c r="H79" t="s">
+        <v>31</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79" t="s">
+        <v>30</v>
+      </c>
+      <c r="K79">
+        <v>135</v>
+      </c>
+      <c r="L79">
+        <v>1.392593</v>
+      </c>
+      <c r="M79">
+        <v>131</v>
+      </c>
+      <c r="N79" t="s">
+        <v>29</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>131</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>44</v>
+      </c>
+      <c r="R79">
+        <v>188</v>
+      </c>
+      <c r="S79">
+        <v>696.80851099999995</v>
+      </c>
+      <c r="T79">
+        <v>1</v>
+      </c>
+      <c r="V79">
+        <v>131</v>
+      </c>
+      <c r="W79">
+        <v>0.53191500000000003</v>
+      </c>
+      <c r="X79">
+        <v>1</v>
+      </c>
+      <c r="Y79">
+        <v>0.53191500000000003</v>
+      </c>
+      <c r="Z79">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>38</v>
+      </c>
+      <c r="B80" t="s">
+        <v>37</v>
+      </c>
+      <c r="C80" t="s">
+        <v>45</v>
+      </c>
+      <c r="D80" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" t="s">
+        <v>41</v>
+      </c>
+      <c r="F80" t="s">
+        <v>33</v>
+      </c>
+      <c r="G80" t="s">
+        <v>32</v>
+      </c>
+      <c r="H80" t="s">
+        <v>31</v>
+      </c>
+      <c r="I80">
+        <v>2</v>
+      </c>
+      <c r="J80" t="s">
+        <v>30</v>
+      </c>
+      <c r="K80">
+        <v>8</v>
+      </c>
+      <c r="L80">
+        <v>1.25</v>
+      </c>
+      <c r="M80">
+        <v>8</v>
+      </c>
+      <c r="N80" t="s">
+        <v>29</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>16</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>44</v>
+      </c>
+      <c r="R80">
+        <v>10</v>
+      </c>
+      <c r="S80">
+        <v>1600</v>
+      </c>
+      <c r="T80">
+        <v>2</v>
+      </c>
+      <c r="V80">
+        <v>8</v>
+      </c>
+      <c r="W80">
+        <v>20</v>
+      </c>
+      <c r="X80">
+        <v>2</v>
+      </c>
+      <c r="Y80">
+        <v>20</v>
+      </c>
+      <c r="Z80">
+        <v>8</v>
+      </c>
+      <c r="AA80">
+        <v>2</v>
+      </c>
+      <c r="AB80">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>38</v>
+      </c>
+      <c r="B81" t="s">
+        <v>37</v>
+      </c>
+      <c r="C81" t="s">
+        <v>45</v>
+      </c>
+      <c r="D81" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" t="s">
+        <v>40</v>
+      </c>
+      <c r="F81" t="s">
+        <v>33</v>
+      </c>
+      <c r="G81" t="s">
+        <v>32</v>
+      </c>
+      <c r="H81" t="s">
+        <v>31</v>
+      </c>
+      <c r="I81">
+        <v>3</v>
+      </c>
+      <c r="J81" t="s">
+        <v>30</v>
+      </c>
+      <c r="K81">
+        <v>138</v>
+      </c>
+      <c r="L81">
+        <v>1.3188409999999999</v>
+      </c>
+      <c r="M81">
+        <v>53</v>
+      </c>
+      <c r="N81" t="s">
+        <v>29</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>159</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>44</v>
+      </c>
+      <c r="R81">
+        <v>182</v>
+      </c>
+      <c r="S81">
+        <v>873.62637400000006</v>
+      </c>
+      <c r="T81">
+        <v>3</v>
+      </c>
+      <c r="V81">
+        <v>53</v>
+      </c>
+      <c r="W81">
+        <v>1.648352</v>
+      </c>
+      <c r="X81">
+        <v>3</v>
+      </c>
+      <c r="Y81">
+        <v>1.648352</v>
+      </c>
+      <c r="Z81">
+        <v>53</v>
+      </c>
+      <c r="AA81">
+        <v>2</v>
+      </c>
+      <c r="AB81">
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>38</v>
+      </c>
+      <c r="B82" t="s">
+        <v>37</v>
+      </c>
+      <c r="C82" t="s">
+        <v>45</v>
+      </c>
+      <c r="D82" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" t="s">
+        <v>34</v>
+      </c>
+      <c r="F82" t="s">
+        <v>33</v>
+      </c>
+      <c r="G82" t="s">
+        <v>32</v>
+      </c>
+      <c r="H82" t="s">
+        <v>31</v>
+      </c>
+      <c r="I82">
+        <v>80</v>
+      </c>
+      <c r="J82" t="s">
+        <v>30</v>
+      </c>
+      <c r="K82">
+        <v>5400</v>
+      </c>
+      <c r="L82">
+        <v>1.4685189999999999</v>
+      </c>
+      <c r="M82">
+        <v>60.325000000000003</v>
+      </c>
+      <c r="N82" t="s">
+        <v>29</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>4826</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R82">
+        <v>7930</v>
+      </c>
+      <c r="S82">
+        <v>608.57503199999996</v>
+      </c>
+      <c r="T82">
+        <v>80</v>
+      </c>
+      <c r="V82">
+        <v>60.325000000000003</v>
+      </c>
+      <c r="W82">
+        <v>1.0088269999999999</v>
+      </c>
+      <c r="X82">
+        <v>91</v>
+      </c>
+      <c r="Y82">
+        <v>1.1475409999999999</v>
+      </c>
+      <c r="Z82">
+        <v>53.032966999999999</v>
+      </c>
+      <c r="AA82">
+        <v>56</v>
+      </c>
+      <c r="AB82">
+        <v>86.178571000000005</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>38</v>
+      </c>
+      <c r="B83" t="s">
+        <v>37</v>
+      </c>
+      <c r="C83" t="s">
+        <v>36</v>
+      </c>
+      <c r="D83" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83" t="s">
+        <v>43</v>
+      </c>
+      <c r="F83" t="s">
+        <v>33</v>
+      </c>
+      <c r="G83" t="s">
+        <v>32</v>
+      </c>
+      <c r="H83" t="s">
+        <v>31</v>
+      </c>
+      <c r="I83">
+        <v>4</v>
+      </c>
+      <c r="J83" t="s">
+        <v>30</v>
+      </c>
+      <c r="K83">
+        <v>253</v>
+      </c>
+      <c r="L83">
+        <v>1.4150199999999999</v>
+      </c>
+      <c r="M83">
+        <v>72.5</v>
+      </c>
+      <c r="N83" t="s">
+        <v>29</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>290</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>28</v>
+      </c>
+      <c r="R83">
+        <v>358</v>
+      </c>
+      <c r="S83">
+        <v>810.05586600000004</v>
+      </c>
+      <c r="T83">
+        <v>4</v>
+      </c>
+      <c r="V83">
+        <v>72.5</v>
+      </c>
+      <c r="W83">
+        <v>1.117318</v>
+      </c>
+      <c r="X83">
+        <v>4</v>
+      </c>
+      <c r="Y83">
+        <v>1.117318</v>
+      </c>
+      <c r="Z83">
+        <v>72.5</v>
+      </c>
+      <c r="AA83">
+        <v>3</v>
+      </c>
+      <c r="AB83">
+        <v>96.666667000000004</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>38</v>
+      </c>
+      <c r="B84" t="s">
+        <v>37</v>
+      </c>
+      <c r="C84" t="s">
+        <v>36</v>
+      </c>
+      <c r="D84" t="s">
+        <v>35</v>
+      </c>
+      <c r="E84" t="s">
+        <v>42</v>
+      </c>
+      <c r="F84" t="s">
+        <v>33</v>
+      </c>
+      <c r="G84" t="s">
+        <v>32</v>
+      </c>
+      <c r="H84" t="s">
+        <v>31</v>
+      </c>
+      <c r="K84">
+        <v>115</v>
+      </c>
+      <c r="L84">
+        <v>1.2434780000000001</v>
+      </c>
+      <c r="N84" t="s">
+        <v>29</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>51</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>28</v>
+      </c>
+      <c r="R84">
+        <v>143</v>
+      </c>
+      <c r="S84">
+        <v>356.64335699999998</v>
+      </c>
+      <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84">
+        <v>0</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>38</v>
+      </c>
+      <c r="B85" t="s">
+        <v>37</v>
+      </c>
+      <c r="C85" t="s">
+        <v>36</v>
+      </c>
+      <c r="D85" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" t="s">
+        <v>41</v>
+      </c>
+      <c r="F85" t="s">
+        <v>33</v>
+      </c>
+      <c r="G85" t="s">
+        <v>32</v>
+      </c>
+      <c r="H85" t="s">
+        <v>31</v>
+      </c>
+      <c r="K85">
+        <v>10</v>
+      </c>
+      <c r="L85">
+        <v>1.3</v>
+      </c>
+      <c r="N85" t="s">
+        <v>29</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>3</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>28</v>
+      </c>
+      <c r="R85">
+        <v>13</v>
+      </c>
+      <c r="S85">
+        <v>230.76923099999999</v>
+      </c>
+      <c r="X85">
+        <v>0</v>
+      </c>
+      <c r="Y85">
+        <v>0</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>38</v>
+      </c>
+      <c r="B86" t="s">
+        <v>37</v>
+      </c>
+      <c r="C86" t="s">
+        <v>36</v>
+      </c>
+      <c r="D86" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" t="s">
+        <v>40</v>
+      </c>
+      <c r="F86" t="s">
+        <v>33</v>
+      </c>
+      <c r="G86" t="s">
+        <v>32</v>
+      </c>
+      <c r="H86" t="s">
+        <v>31</v>
+      </c>
+      <c r="I86">
+        <v>5</v>
+      </c>
+      <c r="J86" t="s">
+        <v>30</v>
+      </c>
+      <c r="K86">
+        <v>186</v>
+      </c>
+      <c r="L86">
+        <v>1.3333330000000001</v>
+      </c>
+      <c r="M86">
+        <v>35</v>
+      </c>
+      <c r="N86" t="s">
+        <v>29</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>175</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>28</v>
+      </c>
+      <c r="R86">
+        <v>248</v>
+      </c>
+      <c r="S86">
+        <v>705.64516100000003</v>
+      </c>
+      <c r="T86">
+        <v>5</v>
+      </c>
+      <c r="V86">
+        <v>35</v>
+      </c>
+      <c r="W86">
+        <v>2.0161289999999998</v>
+      </c>
+      <c r="X86">
+        <v>8</v>
+      </c>
+      <c r="Y86">
+        <v>3.225806</v>
+      </c>
+      <c r="Z86">
+        <v>21.875</v>
+      </c>
+      <c r="AA86">
+        <v>5</v>
+      </c>
+      <c r="AB86">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>38</v>
+      </c>
+      <c r="B87" t="s">
+        <v>37</v>
+      </c>
+      <c r="C87" t="s">
+        <v>36</v>
+      </c>
+      <c r="D87" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" t="s">
+        <v>39</v>
+      </c>
+      <c r="F87" t="s">
+        <v>33</v>
+      </c>
+      <c r="G87" t="s">
+        <v>32</v>
+      </c>
+      <c r="H87" t="s">
+        <v>31</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="N87" t="s">
+        <v>29</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>28</v>
+      </c>
+      <c r="R87">
+        <v>1</v>
+      </c>
+      <c r="S87">
+        <v>0</v>
+      </c>
+      <c r="X87">
+        <v>0</v>
+      </c>
+      <c r="Y87">
+        <v>0</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>38</v>
+      </c>
+      <c r="B88" t="s">
+        <v>37</v>
+      </c>
+      <c r="C88" t="s">
+        <v>36</v>
+      </c>
+      <c r="D88" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" t="s">
+        <v>34</v>
+      </c>
+      <c r="F88" t="s">
+        <v>33</v>
+      </c>
+      <c r="G88" t="s">
+        <v>32</v>
+      </c>
+      <c r="H88" t="s">
+        <v>31</v>
+      </c>
+      <c r="I88">
+        <v>89</v>
+      </c>
+      <c r="J88" t="s">
+        <v>30</v>
+      </c>
+      <c r="K88">
+        <v>4246</v>
+      </c>
+      <c r="L88">
+        <v>1.4335850000000001</v>
+      </c>
+      <c r="M88">
+        <v>47.764044939999998</v>
+      </c>
+      <c r="N88" t="s">
+        <v>29</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>4251</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>28</v>
+      </c>
+      <c r="R88">
+        <v>6087</v>
+      </c>
+      <c r="S88">
+        <v>698.37358300000005</v>
+      </c>
+      <c r="T88">
+        <v>89</v>
+      </c>
+      <c r="V88">
+        <v>47.764045000000003</v>
+      </c>
+      <c r="W88">
+        <v>1.462132</v>
+      </c>
+      <c r="X88">
+        <v>90</v>
+      </c>
+      <c r="Y88">
+        <v>1.478561</v>
+      </c>
+      <c r="Z88">
+        <v>47.233333000000002</v>
+      </c>
+      <c r="AA88">
+        <v>65</v>
+      </c>
+      <c r="AB88">
+        <v>65.400000000000006</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>